--- a/data/trans_dic/IP04D$aparatos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,7; 78,12</t>
+          <t>64,52; 78,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,28; 59,53</t>
+          <t>44,63; 59,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,51; 72,81</t>
+          <t>59,16; 72,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,13; 72,57</t>
+          <t>59,61; 72,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,73; 62,57</t>
+          <t>48,78; 62,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,95; 68,96</t>
+          <t>44,27; 69,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,52; 72,4</t>
+          <t>64,13; 73,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,24; 59,48</t>
+          <t>49,16; 58,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,91; 68,46</t>
+          <t>52,3; 68,18</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,88; 68,48</t>
+          <t>58,47; 69,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,33; 58,94</t>
+          <t>48,83; 59,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,24; 67,51</t>
+          <t>53,24; 67,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,59; 71,36</t>
+          <t>61,48; 71,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,51; 59,07</t>
+          <t>48,45; 59,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,0; 70,23</t>
+          <t>58,4; 69,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,83; 68,42</t>
+          <t>61,22; 68,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,23; 57,78</t>
+          <t>50,46; 57,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,62; 67,31</t>
+          <t>58,78; 67,34</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,7; 76,76</t>
+          <t>64,81; 76,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,36; 51,72</t>
+          <t>39,32; 51,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,62; 82,19</t>
+          <t>61,54; 80,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,62; 72,3</t>
+          <t>60,71; 72,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,94; 48,77</t>
+          <t>35,9; 48,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,46; 64,82</t>
+          <t>50,2; 65,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,52; 73,14</t>
+          <t>64,55; 72,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,56; 48,52</t>
+          <t>39,29; 48,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,58; 71,74</t>
+          <t>57,83; 72,29</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,81; 61,49</t>
+          <t>49,23; 61,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,99; 59,87</t>
+          <t>48,49; 60,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,22; 59,96</t>
+          <t>46,91; 60,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,15; 55,8</t>
+          <t>44,51; 56,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,05; 62,9</t>
+          <t>52,4; 62,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,1; 57,63</t>
+          <t>44,07; 57,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,23; 57,38</t>
+          <t>48,62; 57,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,59; 59,9</t>
+          <t>51,14; 59,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,19; 56,65</t>
+          <t>47,21; 56,73</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,57; 67,45</t>
+          <t>61,42; 67,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,7; 54,71</t>
+          <t>48,77; 54,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,8; 68,11</t>
+          <t>58,66; 67,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,78</t>
+          <t>58,79; 64,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,71; 55,52</t>
+          <t>49,67; 55,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,48; 62,35</t>
+          <t>54,44; 62,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,96; 65,19</t>
+          <t>60,97; 65,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,15; 54,4</t>
+          <t>50,06; 54,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,37; 63,2</t>
+          <t>57,54; 63,67</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>99177</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69201</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77427</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>101701</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82376</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83233</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>200878</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>151577</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>160660</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>89290; 108210</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>59303; 78854</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>69386; 84978</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>92201; 111740</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>72233; 91977</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>62166; 97056</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>187935; 214944</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>138120; 164825</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>134782; 175687</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>130163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>116573</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>148690</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>121600</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>164075</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>278853</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>233274</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>280648</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>119872; 142569</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>100578; 122525</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>100890; 128341</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>137606; 159806</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>108368; 133026</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>148527; 177925</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>262539; 295535</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>216803; 248799</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>260891; 298872</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>110055</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70791</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132117</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>110281</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>106393</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>220336</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>141384</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>238509</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>100696; 118884</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61334; 80606</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>117174; 154029</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>100357; 119642</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>59571; 80180</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>93008; 120520</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>207012; 233327</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>126484; 156221</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>217267; 271575</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>116554</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>110672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89790</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104631</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>115932</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91988</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>221184</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>226604</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>181778</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>103144; 128869</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>99560; 123347</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>78784; 101054</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>92754; 117276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>106020; 126535</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>79465; 104086</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>203189; 238302</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>208484; 242537</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>164416; 197583</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>455948</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>362339</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>415906</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>445689</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>921251</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>752840</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>861595</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>435016; 476483</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>341465; 382945</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>390190; 449372</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>442269; 486898</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>367598; 413510</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>413919; 476641</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>890540; 951405</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>720906; 781491</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>820184; 907555</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$aparatos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,52; 78,19</t>
+          <t>64,87; 78,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,63; 59,35</t>
+          <t>45,47; 59,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,16; 72,46</t>
+          <t>57,9; 72,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,61; 72,24</t>
+          <t>59,31; 72,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,78; 62,11</t>
+          <t>48,63; 62,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,27; 69,12</t>
+          <t>44,69; 69,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,13; 73,34</t>
+          <t>64,08; 73,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,16; 58,67</t>
+          <t>48,69; 59,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,3; 68,18</t>
+          <t>52,47; 68,09</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,47; 69,54</t>
+          <t>57,47; 68,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,83; 59,48</t>
+          <t>49,15; 59,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,24; 67,72</t>
+          <t>54,12; 67,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,48; 71,39</t>
+          <t>60,72; 71,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,45; 59,47</t>
+          <t>48,67; 59,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,4; 69,96</t>
+          <t>59,15; 69,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,22; 68,91</t>
+          <t>61,12; 68,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,46; 57,9</t>
+          <t>50,28; 57,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,78; 67,34</t>
+          <t>58,79; 67,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,81; 76,51</t>
+          <t>64,84; 76,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,32; 51,67</t>
+          <t>39,25; 51,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,54; 80,9</t>
+          <t>61,1; 80,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,71; 72,37</t>
+          <t>60,37; 72,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,9; 48,33</t>
+          <t>37,05; 48,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,2; 65,05</t>
+          <t>49,54; 64,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,55; 72,76</t>
+          <t>64,48; 72,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,29; 48,53</t>
+          <t>39,62; 48,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,83; 72,29</t>
+          <t>57,73; 72,4</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,23; 61,51</t>
+          <t>49,51; 61,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,49; 60,07</t>
+          <t>47,83; 59,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,91; 60,16</t>
+          <t>47,19; 60,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,51; 56,28</t>
+          <t>44,41; 56,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,4; 62,54</t>
+          <t>51,67; 63,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,07; 57,73</t>
+          <t>44,43; 57,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,62; 57,02</t>
+          <t>48,95; 57,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,14; 59,49</t>
+          <t>51,82; 59,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,21; 56,73</t>
+          <t>47,22; 56,21</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,42; 67,27</t>
+          <t>61,24; 67,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,77; 54,69</t>
+          <t>48,64; 54,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,66; 67,56</t>
+          <t>58,92; 68,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58,79; 64,73</t>
+          <t>59,04; 64,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,67; 55,88</t>
+          <t>49,55; 55,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,44; 62,69</t>
+          <t>54,1; 62,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,14</t>
+          <t>60,97; 65,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,06; 54,26</t>
+          <t>50,14; 54,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,67</t>
+          <t>57,7; 63,37</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89290; 108210</t>
+          <t>89774; 108026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59303; 78854</t>
+          <t>60421; 79506</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69386; 84978</t>
+          <t>67901; 85110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92201; 111740</t>
+          <t>91741; 111942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72233; 91977</t>
+          <t>72016; 92902</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62166; 97056</t>
+          <t>62745; 97738</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>187935; 214944</t>
+          <t>187796; 214221</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>138120; 164825</t>
+          <t>136801; 165851</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>134782; 175687</t>
+          <t>135221; 175468</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119872; 142569</t>
+          <t>117835; 140237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100578; 122525</t>
+          <t>101247; 122949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100890; 128341</t>
+          <t>102557; 127400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137606; 159806</t>
+          <t>135917; 159928</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>108368; 133026</t>
+          <t>108878; 133582</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>148527; 177925</t>
+          <t>150442; 176855</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>262539; 295535</t>
+          <t>262118; 292721</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>216803; 248799</t>
+          <t>216055; 248918</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260891; 298872</t>
+          <t>260916; 297807</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>100696; 118884</t>
+          <t>100750; 118600</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61334; 80606</t>
+          <t>61223; 80010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117174; 154029</t>
+          <t>116327; 154041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100357; 119642</t>
+          <t>99806; 119267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59571; 80180</t>
+          <t>61463; 80706</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93008; 120520</t>
+          <t>91788; 119638</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>207012; 233327</t>
+          <t>206765; 232740</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>126484; 156221</t>
+          <t>127542; 157436</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>217267; 271575</t>
+          <t>216902; 271994</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103144; 128869</t>
+          <t>103724; 128187</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>99560; 123347</t>
+          <t>98208; 122670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78784; 101054</t>
+          <t>79264; 101749</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92754; 117276</t>
+          <t>92546; 117317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106020; 126535</t>
+          <t>104537; 127609</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79465; 104086</t>
+          <t>80098; 103750</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>203189; 238302</t>
+          <t>204545; 239731</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>208484; 242537</t>
+          <t>211253; 242922</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>164416; 197583</t>
+          <t>164436; 195747</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>435016; 476483</t>
+          <t>433746; 477138</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>341465; 382945</t>
+          <t>340584; 383439</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>390190; 449372</t>
+          <t>391941; 454634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>442269; 486898</t>
+          <t>444078; 487362</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>367598; 413510</t>
+          <t>366690; 411755</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>413919; 476641</t>
+          <t>411370; 473302</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>890540; 951405</t>
+          <t>890450; 953410</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>720906; 781491</t>
+          <t>722137; 784270</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>820184; 907555</t>
+          <t>822563; 903394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$aparatos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65,75%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55,63%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>62,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>71,67%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>52,08%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66,02%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,63%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,87; 78,06</t>
+          <t>59,13; 72,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,47; 59,84</t>
+          <t>48,73; 62,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,9; 72,57</t>
+          <t>47,92; 70,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,31; 72,37</t>
+          <t>64,7; 78,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,63; 62,74</t>
+          <t>44,28; 59,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,69; 69,61</t>
+          <t>59,48; 73,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,08; 73,09</t>
+          <t>63,52; 72,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,69; 59,03</t>
+          <t>49,24; 59,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,47; 68,09</t>
+          <t>56,77; 70,27</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>63,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>54,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,47; 68,4</t>
+          <t>60,59; 71,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,15; 59,69</t>
+          <t>48,51; 59,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,12; 67,22</t>
+          <t>60,81; 71,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,72; 71,45</t>
+          <t>57,88; 68,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,67; 59,72</t>
+          <t>48,33; 58,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,15; 69,54</t>
+          <t>57,35; 69,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,12; 68,26</t>
+          <t>60,83; 68,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,28; 57,93</t>
+          <t>50,23; 57,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,79; 67,1</t>
+          <t>60,81; 69,32</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42,55%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>58,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>70,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>45,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>69,39%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42,55%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,84; 76,33</t>
+          <t>60,62; 72,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,25; 51,29</t>
+          <t>35,94; 48,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,1; 80,9</t>
+          <t>51,28; 65,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,37; 72,15</t>
+          <t>64,7; 76,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,05; 48,64</t>
+          <t>39,36; 51,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,54; 64,57</t>
+          <t>59,95; 72,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,48; 72,58</t>
+          <t>64,52; 73,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,62; 48,91</t>
+          <t>39,56; 48,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,73; 72,4</t>
+          <t>56,89; 67,03</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>55,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>53,9%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>57,3%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,51; 61,18</t>
+          <t>44,15; 55,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,83; 59,74</t>
+          <t>52,05; 62,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,19; 60,58</t>
+          <t>44,13; 57,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,41; 56,3</t>
+          <t>49,81; 61,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,67; 63,07</t>
+          <t>47,99; 59,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,43; 57,54</t>
+          <t>47,53; 60,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,95; 57,36</t>
+          <t>49,23; 57,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,82; 59,59</t>
+          <t>51,59; 59,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,22; 56,21</t>
+          <t>47,49; 56,69</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61,86%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,24; 67,36</t>
+          <t>59,04; 64,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,64; 54,76</t>
+          <t>49,71; 55,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,92; 68,35</t>
+          <t>56,28; 63,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,04; 64,79</t>
+          <t>61,57; 67,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,55; 55,64</t>
+          <t>48,7; 54,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,1; 62,25</t>
+          <t>59,24; 65,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,28</t>
+          <t>60,96; 65,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,14; 54,46</t>
+          <t>50,15; 54,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,7; 63,37</t>
+          <t>58,67; 63,5</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>131</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>101701</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82376</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78732</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>99177</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>69201</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>77427</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>101701</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82376</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83233</t>
+          <t>80974</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>160660</t>
+          <t>159705</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89774; 108026</t>
+          <t>91459; 112254</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60421; 79506</t>
+          <t>72150; 92652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67901; 85110</t>
+          <t>60329; 89356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91741; 111942</t>
+          <t>89537; 108114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72016; 92902</t>
+          <t>58833; 79096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62745; 97738</t>
+          <t>72014; 89326</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>187796; 214221</t>
+          <t>186151; 212183</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>136801; 165851</t>
+          <t>138331; 167112</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135221; 175468</t>
+          <t>140200; 173540</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>179</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>148690</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>121600</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>156816</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>130163</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>111675</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>116573</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148690</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>121600</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>164075</t>
+          <t>117013</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>280648</t>
+          <t>273829</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>117835; 140237</t>
+          <t>135628; 159723</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101247; 122949</t>
+          <t>108519; 132122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>102557; 127400</t>
+          <t>143870; 169415</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135917; 159928</t>
+          <t>118658; 140406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>108878; 133582</t>
+          <t>99544; 121408</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>150442; 176855</t>
+          <t>105138; 127869</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>262118; 292721</t>
+          <t>260877; 293427</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>216055; 248918</t>
+          <t>215812; 248271</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260916; 297807</t>
+          <t>255356; 291093</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>150</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110281</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98373</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>110055</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>70791</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>132117</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110281</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70594</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>106393</t>
+          <t>104487</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>238509</t>
+          <t>202861</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>100750; 118600</t>
+          <t>100206; 119526</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61223; 80010</t>
+          <t>59631; 80916</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116327; 154041</t>
+          <t>86319; 110967</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99806; 119267</t>
+          <t>100533; 119260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61463; 80706</t>
+          <t>61400; 80679</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91788; 119638</t>
+          <t>94145; 114139</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>206765; 232740</t>
+          <t>206904; 234542</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>127542; 157436</t>
+          <t>127334; 156181</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>216902; 271994</t>
+          <t>185113; 218124</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>129</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>104631</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>115932</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86224</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>116554</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>110672</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>89790</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>104631</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>115932</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91988</t>
+          <t>89747</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>181778</t>
+          <t>175972</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103724; 128187</t>
+          <t>92011; 116283</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98208; 122670</t>
+          <t>105318; 127277</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79264; 101749</t>
+          <t>74315; 97369</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92546; 117317</t>
+          <t>104351; 128826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>104537; 127609</t>
+          <t>98540; 122931</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80098; 103750</t>
+          <t>79449; 100529</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>204545; 239731</t>
+          <t>205748; 239774</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>211253; 242922</t>
+          <t>210301; 244179</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>164436; 195747</t>
+          <t>159352; 190245</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>538</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>589</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>465303</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>433746; 477138</t>
+          <t>444098; 487265</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>340584; 383439</t>
+          <t>367827; 410849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>391941; 454634</t>
+          <t>393508; 445390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>444078; 487362</t>
+          <t>436076; 477724</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>366690; 411755</t>
+          <t>340992; 383063</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>411370; 473302</t>
+          <t>372390; 411409</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>890450; 953410</t>
+          <t>890344; 952094</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>722137; 784270</t>
+          <t>722197; 783510</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>822563; 903394</t>
+          <t>779070; 843161</t>
         </is>
       </c>
     </row>
